--- a/Supplementary_Information/S7_Table_Feature_Comparison.xlsx
+++ b/Supplementary_Information/S7_Table_Feature_Comparison.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Worked_example_aspirin" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,40 +28,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="002E7D32"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00C62828"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00E65100"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -69,41 +47,15 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00002060"/>
-        <bgColor rgb="00002060"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-        <bgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E4F0"/>
-        <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
-        <bgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -113,58 +65,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="001F4E79"/>
+        <color rgb="00A6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="medium">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="001F4E79"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B4C6E7"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="00A6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="00A6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B4C6E7"/>
+        <color rgb="00A6A6A6"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,202 +456,584 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>S7 Table: Feature comparison - PulseTech vs FDA FAERS public dashboard (manuscript Table 7)</t>
-        </is>
-      </c>
+          <t>S7 Table: Feature comparison - PulseTech vs the FDA public FAERS dashboard (titled the AEMS Public Dashboard since March 2026; manuscript Table 7)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>FAERS public dashboard</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>PulseTech</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>How the public dashboard does it</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>How PulseTech does it</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Where the PulseTech capability is documented</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>In-UI PRR/ROR/IC/EBGM</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Counts and percentages of cases by reaction for a searched product; no disproportionality measure</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>For each drug-ADR pair with n11 &gt;= 3 in the selected bands, builds the 2x2 table and computes PRR (with chi-squared), ROR with 95% CI, IC with IC025 and EBGM with EB05; flags a Signal when any criterion is met (S5 Table)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Signal Detection module (Fig 2); Methods - Classical disproportionality analysis</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>ICH E11 age bands as analysis denominator</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Seven age groups (0-1 month, 2 months-2 years, 3-11 years, 12-17 years, 18-64, 65-85, over 85 years) plus Not specified, used to count reports</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Five bands (Neonate &lt;28 days, Infant &lt;2 years, Child &lt;12 years, Adolescent &lt;18 years, Unknown); every statistic is computed within the selected bands and the Unknown band stays visible</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Table 2; Table 4 Step 4</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Interactive drug-ADR graph view</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>GNN Network View (Figs 6 and 7)</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Tables and stacked bar charts</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>HANConv network view of drug, ADR and cohort nodes with flagged signal edges and ranked candidate links for review</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>GNN Network View (Figs 6 and 7); Table 12; Table 13</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Human-gated ingestion (quality gate)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Data loaded and maintained by the FDA</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>13-step pipeline; Step 13 shows a preview that a reviewer approves or rejects, and only approved data are written to the database</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Table 4 Step 13</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>One-click PDF report export</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>On-screen tables and charts with data download (authors' review)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Report Builder: the analyst selects sections and exports a formatted PDF</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Report Builder (Fig 9)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Raw reporting-frequency browsing</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Reports by year, report type, reporter, reporter region, seriousness, age group and sex; product search by reaction, product name, generic name, age group, sex and reporter type; reaction groups by System Organ Class</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Demographics, ADR Analysis and Outcomes modules for the loaded quarters and selected bands</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Demographics, ADR Analysis and Outcomes modules (Figs 4, 5 and 8)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Regulator-maintained, all-drug coverage</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>All drugs and biologics, all ages, all years, maintained by the FDA</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>FAERS quarterly files 2021Q1-2025Q4 loaded by the analyst; designed for pediatric review</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Results - Comparing PulseTech with the public FAERS dashboard</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>S7 Table (continued): the same drug in both tools - aspirin</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Tool and view</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Public dashboard, aspirin search (all years, all ages)</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Total cases</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>131,182</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Authors' extraction, 2026; the dashboard is updated continuously, so current values differ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Public dashboard, aspirin search (all years, all ages)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Most frequent reactions</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Gastrointestinal haemorrhage 16,659 (12.70%); anaemia 6,881 (5.25%); dyspnoea 5,531 (4.22%)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Counts and shares of cases; no disproportionality measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Public dashboard, aspirin search (all years, all ages)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Cases by pediatric age group</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0-1 month 218; 2 months-2 years 588; 3-11 years 842; 12-17 years 1,201</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>24,569 cases (18.73%) have no age specified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>PulseTech, Q1 2025 signal cache, four resolved pediatric bands (S8 Table)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>NEONATE - Foetal exposure during pregnancy</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>n11 5; PRR 2.46; ROR n/a; IC025 -0.92; EB05 0.90; Signal (PRR)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Term category: exposure, overdose or poisoning; not on the label (SIDER 4.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>PulseTech, Q1 2025 signal cache, four resolved pediatric bands (S8 Table)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>NEONATE - Premature baby</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>n11 4; PRR 4.62; ROR 19.11 (lower 2.12); IC025 -0.54; EB05 0.97; Signal (PRR, ROR)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Clinical event; not on the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>PulseTech, Q1 2025 signal cache, four resolved pediatric bands (S8 Table)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>CHILD - Drug ineffective</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>n11 3; PRR 9.99; ROR 23.47 (lower 3.91); IC025 -0.42; EB05 1.68; Signal (PRR, ROR)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Term category: lack of effect; not on the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>PulseTech, Q1 2025 signal cache, four resolved pediatric bands (S8 Table)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ADOLESCENT - Toxicity to various agents</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>n11 3; PRR 20.11; ROR 25.84 (lower 7.07); IC025 -0.12; EB05 2.23; Signal (PRR, ROR, EB05)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Term category: exposure, overdose or poisoning; related term on the label</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>What the comparison shows</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>The dashboard shows what is reported most often for aspirin across all ages; PulseTech shows which aspirin pairs are reported disproportionately often within each pediatric band. All four flagged aspirin pairs are exposure, prematurity, lack-of-effect or toxicity terms rather than labelled reactions, which is why every flag goes to an analyst for review (Results - Comparison with drug labels)</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>S7 Table: notes</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Source of the dashboard description</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Authors' review of the FDA public dashboard (Qlik Sense application at fis.fda.gov), 2026. Since 11 March 2026 the FDA has titled it the Adverse Event Monitoring System (AEMS) Public Dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Source of the PulseTech values</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>S8 Table (Q1 2025 signal cache, primary-suspect role); term categories and label status as defined for S9 Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Not compared</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Other systems (VigiBase/VigiLyze, EudraVigilance/EVDAS, OpenVigil) are not compared here because their features could not be verified from public documentation for this study</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Supplementary_Information/S7_Table_Feature_Comparison.xlsx
+++ b/Supplementary_Information/S7_Table_Feature_Comparison.xlsx
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>In-UI PRR/ROR/IC/EBGM</t>
+          <t>In-dashboard PRR/ROR/IC/EBGM</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Five bands (Neonate &lt;28 days, Infant &lt;2 years, Child &lt;12 years, Adolescent &lt;18 years, Unknown); every statistic is computed within the selected bands and the Unknown band stays visible</t>
+          <t>Four ICH E11(R1) bands (Neonate &lt;28 days, Infant &lt;2 years, Child &lt;12 years, Adolescent &lt;18 years) plus an Unknown category; every statistic is computed within the selected bands and the Unknown category stays visible</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
